--- a/tests/mung/fixtures/sumprod.xlsx
+++ b/tests/mung/fixtures/sumprod.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\fixtures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\mung\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C560B14D-D045-4165-9DC1-73F6B5CCD1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B4A508-9917-4C18-B2EF-A313F3D03B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="3120" windowWidth="28800" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data1" sheetId="1" r:id="rId1"/>
@@ -113,9 +113,6 @@
     <t>concept_add</t>
   </si>
   <si>
-    <t>concept_from</t>
-  </si>
-  <si>
     <t>fstype</t>
   </si>
   <si>
@@ -192,6 +189,9 @@
   </si>
   <si>
     <t>concept_total</t>
+  </si>
+  <si>
+    <t>concept_addend</t>
   </si>
 </sst>
 </file>
@@ -370,7 +370,7 @@
   <autoFilter ref="A1:D27" xr:uid="{5D7EFAE3-F87F-4064-85C3-9BBC1CE4994A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{412D6112-857C-4CBE-9800-D1870FF2BA72}" name="concept_add"/>
-    <tableColumn id="2" xr3:uid="{FC770A68-4966-4AB5-A624-4B95C294D977}" name="concept_from"/>
+    <tableColumn id="2" xr3:uid="{FC770A68-4966-4AB5-A624-4B95C294D977}" name="concept_addend"/>
     <tableColumn id="3" xr3:uid="{B535511B-AC74-4091-831D-AC01DFEF237A}" name="fstype"/>
     <tableColumn id="4" xr3:uid="{2402D9C5-6A76-4662-BBF4-381D73B61B32}" name="coef"/>
   </tableColumns>
@@ -1897,7 +1897,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1911,13 +1911,13 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2">
         <v>1000</v>
       </c>
       <c r="F2" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D2,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D2,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -1932,13 +1932,13 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>150</v>
       </c>
       <c r="F3" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D3,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D3,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -1953,13 +1953,13 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>50</v>
       </c>
       <c r="F4" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D4,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D4,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -1974,13 +1974,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>200</v>
       </c>
       <c r="F5" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D5,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D5,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         <v>150</v>
       </c>
       <c r="F6" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D6,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D6,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2016,13 +2016,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7">
         <v>-10</v>
       </c>
       <c r="F7" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D7,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D7,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
         <v>125</v>
       </c>
       <c r="F8" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D8,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D8,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2058,13 +2058,13 @@
         <v>10</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D9,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D9,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>1000</v>
       </c>
       <c r="F10" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D10,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D10,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2100,13 +2100,13 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>150</v>
       </c>
       <c r="F11" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D11,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D11,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D12,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D12,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>200</v>
       </c>
       <c r="F13" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D13,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D13,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2160,13 +2160,13 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14">
         <v>1000</v>
       </c>
       <c r="F14" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D14,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D14,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2181,13 +2181,13 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D15,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D15,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2202,10 +2202,10 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D16,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D16,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2220,13 +2220,13 @@
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17">
         <v>200</v>
       </c>
       <c r="F17" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D17,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D17,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="F18" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D18,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D18,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2259,13 +2259,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19">
         <v>-10</v>
       </c>
       <c r="F19" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D19,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D19,concepts_adds[concept_addend],0))</f>
         <v>EbitdaExclUnusalAndExtraordinary</v>
       </c>
     </row>
@@ -2280,13 +2280,13 @@
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20">
         <v>1000</v>
       </c>
       <c r="F20" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D20,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D20,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2301,13 +2301,13 @@
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>150</v>
       </c>
       <c r="F21" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D21,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D21,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2322,13 +2322,13 @@
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22">
         <v>50</v>
       </c>
       <c r="F22" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D22,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D22,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2343,13 +2343,13 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23">
         <v>200</v>
       </c>
       <c r="F23" t="str">
-        <f>INDEX(concepts_adds[concept_add], MATCH(D23,concepts_adds[concept_from],0))</f>
+        <f>INDEX(concepts_adds[concept_add], MATCH(D23,concepts_adds[concept_addend],0))</f>
         <v>AssetsNongoodwillNoncash</v>
       </c>
     </row>
@@ -2372,24 +2372,24 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>30</v>
-      </c>
-      <c r="D1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2400,10 +2400,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2411,13 +2411,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2425,13 +2425,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2439,13 +2439,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2453,13 +2453,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -2470,10 +2470,10 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -2481,13 +2481,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -2498,10 +2498,10 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>-1</v>
@@ -2509,13 +2509,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -2540,10 +2540,10 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -2554,10 +2554,10 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -2565,13 +2565,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2579,13 +2579,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2607,13 +2607,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2621,13 +2621,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2635,13 +2635,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2663,13 +2663,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
         <v>47</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2677,13 +2677,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2691,13 +2691,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2719,13 +2719,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2733,13 +2733,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>1</v>
